--- a/artfynd/A 33141-2026 artfynd.xlsx
+++ b/artfynd/A 33141-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191691</v>
       </c>
       <c r="B2" t="n">
-        <v>97567</v>
+        <v>97568</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136191690</v>
       </c>
       <c r="B3" t="n">
-        <v>93071</v>
+        <v>93072</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33141-2026 artfynd.xlsx
+++ b/artfynd/A 33141-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191691</v>
       </c>
       <c r="B2" t="n">
-        <v>97568</v>
+        <v>97569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136191690</v>
       </c>
       <c r="B3" t="n">
-        <v>93072</v>
+        <v>93073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136191688</v>
       </c>
       <c r="B4" t="n">
-        <v>75534</v>
+        <v>75535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136191692</v>
       </c>
       <c r="B5" t="n">
-        <v>75534</v>
+        <v>75535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>136191694</v>
       </c>
       <c r="B6" t="n">
-        <v>75534</v>
+        <v>75535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33141-2026 artfynd.xlsx
+++ b/artfynd/A 33141-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191691</v>
       </c>
       <c r="B2" t="n">
-        <v>97569</v>
+        <v>97575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136191690</v>
       </c>
       <c r="B3" t="n">
-        <v>93073</v>
+        <v>93079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136191688</v>
       </c>
       <c r="B4" t="n">
-        <v>75535</v>
+        <v>75539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136191692</v>
       </c>
       <c r="B5" t="n">
-        <v>75535</v>
+        <v>75539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>136191694</v>
       </c>
       <c r="B6" t="n">
-        <v>75535</v>
+        <v>75539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33141-2026 artfynd.xlsx
+++ b/artfynd/A 33141-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136191691</v>
+        <v>136327534</v>
       </c>
       <c r="B2" t="n">
-        <v>97575</v>
+        <v>96734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lunnebomossen, Dls</t>
+          <t>Lunnebomossen, N om, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>342918</v>
+        <v>342530</v>
       </c>
       <c r="R2" t="n">
-        <v>6523118</v>
+        <v>6523067</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,62 +749,63 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Troligt protonema av Buxbaumia viridis.</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre nygallrad barrskog.</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Låga av barrträd.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136191691</t>
+          <t>https://artportalen.se/Sighting/136327534</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136191690</v>
+        <v>136191691</v>
       </c>
       <c r="B3" t="n">
-        <v>93079</v>
+        <v>97576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4786</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>342876</v>
+        <v>342918</v>
       </c>
       <c r="R3" t="n">
-        <v>6523101</v>
+        <v>6523118</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,6 +884,21 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -893,38 +913,38 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136191690</t>
+          <t>https://artportalen.se/Sighting/136191691</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136191688</v>
+        <v>136191690</v>
       </c>
       <c r="B4" t="n">
-        <v>75539</v>
+        <v>93080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>4786</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>342923</v>
+        <v>342876</v>
       </c>
       <c r="R4" t="n">
-        <v>6523137</v>
+        <v>6523101</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,21 +1001,6 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1010,16 +1015,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136191688</t>
+          <t>https://artportalen.se/Sighting/136191690</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136191692</v>
+        <v>136191688</v>
       </c>
       <c r="B5" t="n">
-        <v>75539</v>
+        <v>75540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>342955</v>
+        <v>342923</v>
       </c>
       <c r="R5" t="n">
-        <v>6523133</v>
+        <v>6523137</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1127,16 +1132,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136191692</t>
+          <t>https://artportalen.se/Sighting/136191688</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136191694</v>
+        <v>136191692</v>
       </c>
       <c r="B6" t="n">
-        <v>75539</v>
+        <v>75540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>343010</v>
+        <v>342955</v>
       </c>
       <c r="R6" t="n">
-        <v>6523136</v>
+        <v>6523133</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1244,7 +1249,245 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136191692</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136191694</v>
+      </c>
+      <c r="B7" t="n">
+        <v>75540</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lunnebomossen, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>343010</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6523136</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136191694</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136327601</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75540</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lundeb, ca 120 m V om Svartetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>342963</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6523136</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Gammal gran. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136327601</t>
         </is>
       </c>
     </row>
@@ -1255,6 +1498,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33141-2026 artfynd.xlsx
+++ b/artfynd/A 33141-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136327534</v>
       </c>
       <c r="B2" t="n">
-        <v>96734</v>
+        <v>96745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136191691</v>
       </c>
       <c r="B3" t="n">
-        <v>97576</v>
+        <v>97587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136191690</v>
       </c>
       <c r="B4" t="n">
-        <v>93080</v>
+        <v>93086</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136191688</v>
       </c>
       <c r="B5" t="n">
-        <v>75540</v>
+        <v>75544</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136191692</v>
       </c>
       <c r="B6" t="n">
-        <v>75540</v>
+        <v>75544</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136191694</v>
       </c>
       <c r="B7" t="n">
-        <v>75540</v>
+        <v>75544</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136327601</v>
       </c>
       <c r="B8" t="n">
-        <v>75540</v>
+        <v>75544</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 33141-2026 artfynd.xlsx
+++ b/artfynd/A 33141-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136327534</v>
       </c>
       <c r="B2" t="n">
-        <v>96745</v>
+        <v>96758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136191691</v>
       </c>
       <c r="B3" t="n">
-        <v>97587</v>
+        <v>97600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136191690</v>
       </c>
       <c r="B4" t="n">
-        <v>93086</v>
+        <v>93093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136191688</v>
       </c>
       <c r="B5" t="n">
-        <v>75544</v>
+        <v>75550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136191692</v>
       </c>
       <c r="B6" t="n">
-        <v>75544</v>
+        <v>75550</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136191694</v>
       </c>
       <c r="B7" t="n">
-        <v>75544</v>
+        <v>75550</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136327601</v>
       </c>
       <c r="B8" t="n">
-        <v>75544</v>
+        <v>75550</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 33141-2026 artfynd.xlsx
+++ b/artfynd/A 33141-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136327534</v>
       </c>
       <c r="B2" t="n">
-        <v>96758</v>
+        <v>96759</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136191691</v>
       </c>
       <c r="B3" t="n">
-        <v>97600</v>
+        <v>97601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136191690</v>
       </c>
       <c r="B4" t="n">
-        <v>93093</v>
+        <v>93094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33141-2026 artfynd.xlsx
+++ b/artfynd/A 33141-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136327534</v>
       </c>
       <c r="B2" t="n">
-        <v>96759</v>
+        <v>96772</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136191691</v>
       </c>
       <c r="B3" t="n">
-        <v>97601</v>
+        <v>97614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136191690</v>
       </c>
       <c r="B4" t="n">
-        <v>93094</v>
+        <v>93107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136191688</v>
       </c>
       <c r="B5" t="n">
-        <v>75550</v>
+        <v>75563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136191692</v>
       </c>
       <c r="B6" t="n">
-        <v>75550</v>
+        <v>75563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136191694</v>
       </c>
       <c r="B7" t="n">
-        <v>75550</v>
+        <v>75563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136327601</v>
       </c>
       <c r="B8" t="n">
-        <v>75550</v>
+        <v>75563</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 33141-2026 artfynd.xlsx
+++ b/artfynd/A 33141-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136327534</v>
       </c>
       <c r="B2" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136191691</v>
       </c>
       <c r="B3" t="n">
-        <v>97614</v>
+        <v>97615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136191690</v>
       </c>
       <c r="B4" t="n">
-        <v>93107</v>
+        <v>93108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136191688</v>
       </c>
       <c r="B5" t="n">
-        <v>75563</v>
+        <v>75564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136191692</v>
       </c>
       <c r="B6" t="n">
-        <v>75563</v>
+        <v>75564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136191694</v>
       </c>
       <c r="B7" t="n">
-        <v>75563</v>
+        <v>75564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136327601</v>
       </c>
       <c r="B8" t="n">
-        <v>75563</v>
+        <v>75564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
